--- a/docs/data/beidan_26087_dashboard.xlsx
+++ b/docs/data/beidan_26087_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26087期 比赛看板（皇冠历史相同亚盘） — 2026-08-21</t>
+          <t>⚽ 北京单场26087期 比赛看板（皇冠历史相同亚盘） — 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -700,10 +704,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -756,10 +764,14 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -812,10 +824,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -868,10 +884,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -924,10 +944,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -980,10 +1004,14 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1036,10 +1064,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1092,10 +1124,14 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1148,10 +1184,14 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1204,10 +1244,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1260,10 +1304,14 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1316,10 +1364,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1372,10 +1424,14 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1428,10 +1484,14 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1484,10 +1544,14 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1540,10 +1604,14 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -1596,10 +1664,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1652,10 +1724,14 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1708,10 +1784,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1764,10 +1844,14 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1820,10 +1904,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1876,10 +1964,14 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1932,10 +2024,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1988,10 +2084,14 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -2044,10 +2144,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -2100,10 +2204,14 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2156,10 +2264,14 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2212,10 +2324,14 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
+          <t>5:2</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2268,10 +2384,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2324,10 +2444,14 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2380,10 +2504,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2436,10 +2564,14 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2492,10 +2624,14 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2548,10 +2684,14 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2604,10 +2744,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2660,10 +2804,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2716,10 +2864,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2772,10 +2924,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
+          <t>5:3</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2828,10 +2984,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -2884,10 +3044,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -2940,10 +3104,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2996,10 +3164,14 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -3052,10 +3224,14 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -3108,10 +3284,14 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -3164,10 +3344,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>两球</t>
@@ -3220,10 +3404,14 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3276,10 +3464,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3332,10 +3524,14 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3388,10 +3584,14 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -3444,10 +3644,14 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -3500,10 +3704,14 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -3556,10 +3764,14 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -3612,10 +3824,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -3668,10 +3884,14 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -3724,10 +3944,14 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -3780,10 +4004,14 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -3836,10 +4064,14 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -3892,10 +4124,14 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -3948,10 +4184,14 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4004,10 +4244,14 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4060,10 +4304,14 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4116,10 +4364,14 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4172,10 +4424,14 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4228,10 +4484,14 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4284,10 +4544,14 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -4340,10 +4604,14 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4396,10 +4664,14 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4452,10 +4724,14 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4508,10 +4784,14 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4564,10 +4844,14 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -4620,10 +4904,14 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr"/>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -4676,10 +4964,14 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -4732,10 +5024,14 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -4788,10 +5084,14 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr"/>
+          <t>0:7</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -4844,10 +5144,14 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -4900,10 +5204,14 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -4956,10 +5264,14 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5012,10 +5324,14 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5068,10 +5384,14 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -5124,10 +5444,14 @@
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -5180,10 +5504,14 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -5236,10 +5564,14 @@
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -5292,10 +5624,14 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -5348,10 +5684,14 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -5404,10 +5744,14 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5460,10 +5804,14 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5516,10 +5864,14 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -5572,10 +5924,14 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -5628,10 +5984,14 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr"/>
+          <t>5:3</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -5684,10 +6044,14 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -5740,10 +6104,14 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -5796,10 +6164,14 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -5852,10 +6224,14 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr"/>
+          <t>2:5</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -5908,10 +6284,14 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -5964,10 +6344,14 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6020,10 +6404,14 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6076,10 +6464,14 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6132,10 +6524,14 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6188,10 +6584,14 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6244,10 +6644,14 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6300,10 +6704,14 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -6356,10 +6764,14 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -6412,10 +6824,14 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6468,10 +6884,14 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -6524,10 +6944,14 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6580,10 +7004,14 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -6636,10 +7064,14 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6692,10 +7124,14 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -6748,10 +7184,14 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -6804,10 +7244,14 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6860,10 +7304,14 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -6916,10 +7364,14 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I116" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -6972,10 +7424,14 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H117" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7028,10 +7484,14 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7084,10 +7544,14 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7140,10 +7604,14 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -7196,10 +7664,14 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7252,10 +7724,14 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7308,10 +7784,14 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7364,10 +7844,14 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7420,10 +7904,14 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -7476,10 +7964,14 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I126" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7532,10 +8024,14 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -7588,10 +8084,14 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -7644,10 +8144,14 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -7700,10 +8204,14 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -7756,10 +8264,14 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -7812,10 +8324,14 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I132" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -7868,10 +8384,14 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -7924,10 +8444,14 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I134" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -7980,10 +8504,14 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -8036,10 +8564,14 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I136" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8092,10 +8624,14 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8148,10 +8684,14 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8204,10 +8744,14 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -8260,10 +8804,14 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8316,10 +8864,14 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -8372,10 +8924,14 @@
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -8428,10 +8984,14 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H143" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -8484,10 +9044,14 @@
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8540,10 +9104,14 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8596,10 +9164,14 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -8652,10 +9224,14 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="5" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -8708,10 +9284,14 @@
       </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -8764,10 +9344,14 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H149" s="5" t="inlineStr"/>
+          <t>5:2</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -8820,10 +9404,14 @@
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8876,10 +9464,14 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -8932,10 +9524,14 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -8988,10 +9584,14 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9044,10 +9644,14 @@
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr"/>
+          <t>4:3</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -9100,10 +9704,14 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9156,10 +9764,14 @@
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -9212,10 +9824,14 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -9268,10 +9884,14 @@
       </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9324,10 +9944,14 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -9380,10 +10004,14 @@
       </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I160" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9436,10 +10064,14 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H161" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9492,10 +10124,14 @@
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -9548,10 +10184,14 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -9604,10 +10244,14 @@
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -9660,10 +10304,14 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H165" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -9716,10 +10364,14 @@
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -9772,10 +10424,14 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -9828,10 +10484,14 @@
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I168" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -9884,10 +10544,14 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -9940,10 +10604,14 @@
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -9996,10 +10664,14 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -10032,7 +10704,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>08-22 23:00</t>
+          <t>08-23 02:00</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -10052,24 +10724,32 @@
       </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr"/>
-      <c r="I172" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>球半/两球</t>
+        </is>
+      </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>21%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>32%</t>
         </is>
       </c>
     </row>
@@ -10104,10 +10784,14 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="5" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10160,10 +10844,14 @@
       </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -10216,10 +10904,14 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -10252,7 +10944,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>08-23 03:00</t>
+          <t>08-23 02:30</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -10272,10 +10964,14 @@
       </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -10328,10 +11024,14 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -10384,10 +11084,14 @@
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10440,10 +11144,14 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H179" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -10496,10 +11204,14 @@
       </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -10552,10 +11264,14 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -10608,10 +11324,14 @@
       </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10664,10 +11384,14 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H183" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10720,10 +11444,14 @@
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10776,10 +11504,14 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H185" s="5" t="inlineStr"/>
+          <t>4:4</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -10832,10 +11564,14 @@
       </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10888,10 +11624,14 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H187" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -10944,10 +11684,14 @@
       </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H188" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -11000,10 +11744,14 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H189" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -11056,10 +11804,14 @@
       </c>
       <c r="G190" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H190" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -11112,10 +11864,14 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H191" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -11168,10 +11924,14 @@
       </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H192" s="4" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -11224,10 +11984,14 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H193" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -11280,10 +12044,14 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H194" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11336,10 +12104,14 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H195" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
           <t>两球</t>
@@ -11392,10 +12164,14 @@
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -11448,10 +12224,14 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11504,10 +12284,14 @@
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -11560,10 +12344,14 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" s="5" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I199" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11596,7 +12384,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>08-23 07:07</t>
+          <t>08-23 09:30</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -11616,10 +12404,14 @@
       </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="inlineStr"/>
+          <t>5:2</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -11652,7 +12444,7 @@
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>08-23 07:30</t>
+          <t>08-23 07:40</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
@@ -11672,10 +12464,14 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H201" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I201" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -11708,7 +12504,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>08-23 07:30</t>
+          <t>08-23 07:40</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -11728,10 +12524,14 @@
       </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -11764,7 +12564,7 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>08-23 07:30</t>
+          <t>08-23 07:40</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
@@ -11784,10 +12584,14 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I203" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -11820,7 +12624,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>08-23 07:30</t>
+          <t>08-23 07:40</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -11840,10 +12644,14 @@
       </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H204" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -11876,7 +12684,7 @@
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>08-23 07:30</t>
+          <t>08-23 07:40</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
@@ -11896,10 +12704,14 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H205" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -11932,7 +12744,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>08-23 07:30</t>
+          <t>08-23 07:40</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -11952,10 +12764,14 @@
       </c>
       <c r="G206" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H206" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I206" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -12008,10 +12824,14 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H207" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I207" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -12064,10 +12884,14 @@
       </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H208" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I208" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12120,10 +12944,14 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H209" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I209" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -12156,7 +12984,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>08-23 08:30</t>
+          <t>08-23 09:10</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -12176,24 +13004,32 @@
       </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H210" s="4" t="inlineStr"/>
-      <c r="I210" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
@@ -12208,7 +13044,7 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>08-23 08:30</t>
+          <t>08-23 08:40</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
@@ -12228,14 +13064,22 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H211" s="5" t="inlineStr"/>
-      <c r="I211" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
       <c r="J211" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="K211" s="5" t="inlineStr">
@@ -12245,7 +13089,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
@@ -12260,7 +13104,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>08-23 08:30</t>
+          <t>08-23 08:40</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -12280,10 +13124,14 @@
       </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H212" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12336,10 +13184,14 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H213" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -12372,7 +13224,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>08-23 09:30</t>
+          <t>08-23 09:40</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -12428,7 +13280,7 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>08-23 10:30</t>
+          <t>08-23 10:40</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
@@ -12484,7 +13336,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>08-23 10:30</t>
+          <t>08-23 10:40</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -12540,7 +13392,7 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>08-23 10:30</t>
+          <t>08-23 10:40</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
@@ -14916,20 +15768,24 @@
         </is>
       </c>
       <c r="H259" s="5" t="inlineStr"/>
-      <c r="I259" s="5" t="inlineStr"/>
+      <c r="I259" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
       <c r="J259" s="7" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="K259" s="5" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>26%</t>
         </is>
       </c>
     </row>
@@ -14968,20 +15824,24 @@
         </is>
       </c>
       <c r="H260" s="4" t="inlineStr"/>
-      <c r="I260" s="4" t="inlineStr"/>
+      <c r="I260" s="4" t="inlineStr">
+        <is>
+          <t>受半球</t>
+        </is>
+      </c>
       <c r="J260" s="4" t="inlineStr">
         <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="K260" s="4" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="L260" s="4" t="inlineStr">
+        <is>
           <t>38%</t>
-        </is>
-      </c>
-      <c r="K260" s="4" t="inlineStr">
-        <is>
-          <t>29%</t>
-        </is>
-      </c>
-      <c r="L260" s="4" t="inlineStr">
-        <is>
-          <t>32%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26087_dashboard.xlsx
+++ b/docs/data/beidan_26087_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26087期 比赛看板（皇冠历史相同亚盘） — 2026-08-23</t>
+          <t>⚽ 北京单场26087期 比赛看板（皇冠历史相同亚盘） — 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13244,10 +13244,14 @@
       </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H214" s="4" t="inlineStr"/>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I214" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -13300,10 +13304,14 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H215" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I215" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -13356,10 +13364,14 @@
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H216" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13412,10 +13424,14 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H217" s="5" t="inlineStr"/>
+          <t>1:5</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -13468,10 +13484,14 @@
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H218" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I218" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -13524,10 +13544,14 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H219" s="5" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I219" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -13580,10 +13604,14 @@
       </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H220" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I220" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -13636,10 +13664,14 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H221" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I221" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -13692,10 +13724,14 @@
       </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H222" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -13748,10 +13784,14 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H223" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -13804,10 +13844,14 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H224" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -13860,10 +13904,14 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H225" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I225" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -13916,10 +13964,14 @@
       </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H226" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -13972,10 +14024,14 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H227" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I227" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -14028,10 +14084,14 @@
       </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H228" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14084,10 +14144,14 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H229" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I229" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -14140,10 +14204,14 @@
       </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H230" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14196,10 +14264,14 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H231" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I231" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14252,10 +14324,14 @@
       </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H232" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I232" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -14308,10 +14384,14 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I233" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -14364,10 +14444,14 @@
       </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H234" s="4" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I234" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -14420,10 +14504,14 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H235" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I235" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -14476,10 +14564,14 @@
       </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H236" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H236" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I236" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -14532,10 +14624,14 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H237" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I237" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14588,10 +14684,14 @@
       </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I238" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -14644,10 +14744,14 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="inlineStr"/>
+          <t>2:3</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I239" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -14700,10 +14804,14 @@
       </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H240" s="4" t="inlineStr"/>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I240" s="4" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -14756,10 +14864,14 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H241" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I241" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -14812,10 +14924,14 @@
       </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H242" s="4" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H242" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I242" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -14868,10 +14984,14 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H243" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I243" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -14924,10 +15044,14 @@
       </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H244" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H244" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I244" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -14980,10 +15104,14 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H245" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -15036,10 +15164,14 @@
       </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H246" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H246" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I246" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -15092,10 +15224,14 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H247" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I247" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -15148,10 +15284,14 @@
       </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H248" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H248" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I248" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -15204,10 +15344,14 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H249" s="5" t="inlineStr"/>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -15260,10 +15404,14 @@
       </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H250" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I250" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -15316,10 +15464,14 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H251" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -15372,10 +15524,14 @@
       </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H252" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I252" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -15428,10 +15584,14 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H253" s="5" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H253" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -15484,10 +15644,14 @@
       </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H254" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I254" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -15520,7 +15684,7 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>08-23 22:45</t>
+          <t>08-23 23:15</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
@@ -15540,10 +15704,14 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H255" s="5" t="inlineStr"/>
+          <t>2:5</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
           <t>受球半</t>
@@ -15596,10 +15764,14 @@
       </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H256" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I256" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -15652,10 +15824,14 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H257" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H257" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -15708,10 +15884,14 @@
       </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H258" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I258" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -15764,10 +15944,14 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H259" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H259" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -15820,10 +16004,14 @@
       </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H260" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I260" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -15876,10 +16064,14 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H261" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H261" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -15932,10 +16124,14 @@
       </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H262" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I262" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -15988,10 +16184,14 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H263" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H263" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I263" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -16044,10 +16244,14 @@
       </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H264" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I264" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -16100,10 +16304,14 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H265" s="5" t="inlineStr"/>
+          <t>5:0</t>
+        </is>
+      </c>
+      <c r="H265" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I265" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -16156,10 +16364,14 @@
       </c>
       <c r="G266" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H266" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I266" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -16212,10 +16424,14 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" s="5" t="inlineStr"/>
+          <t>3:3</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I267" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -16268,10 +16484,14 @@
       </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H268" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I268" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -16324,10 +16544,14 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H269" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H269" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I269" s="5" t="inlineStr">
         <is>
           <t>受一球/球半</t>
@@ -16380,10 +16604,14 @@
       </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H270" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I270" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16436,10 +16664,14 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H271" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I271" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -16492,10 +16724,14 @@
       </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H272" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I272" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -16548,10 +16784,14 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I273" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -16604,10 +16844,14 @@
       </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H274" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I274" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16660,10 +16904,14 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I275" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -16716,10 +16964,14 @@
       </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I276" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -16772,10 +17024,14 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H277" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H277" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I277" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -16828,10 +17084,14 @@
       </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H278" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I278" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -16884,10 +17144,14 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I279" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -16940,10 +17204,14 @@
       </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H280" s="4" t="inlineStr"/>
+          <t>3:5</t>
+        </is>
+      </c>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I280" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -16996,10 +17264,14 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H281" s="5" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H281" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I281" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -17052,10 +17324,14 @@
       </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H282" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H282" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I282" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -17108,10 +17384,14 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H283" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I283" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -17164,10 +17444,14 @@
       </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H284" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H284" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I284" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -17220,10 +17504,14 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H285" s="5" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H285" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I285" s="5" t="inlineStr">
         <is>
           <t>球半</t>
@@ -17276,24 +17564,32 @@
       </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H286" s="4" t="inlineStr"/>
-      <c r="I286" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H286" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
       <c r="J286" s="4" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="K286" s="4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>12%</t>
         </is>
       </c>
     </row>
@@ -17328,10 +17624,14 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H287" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H287" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I287" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -17384,10 +17684,14 @@
       </c>
       <c r="G288" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H288" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H288" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I288" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -17440,10 +17744,14 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H289" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I289" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -17496,10 +17804,14 @@
       </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H290" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H290" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I290" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -17552,10 +17864,14 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H291" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -17608,10 +17924,14 @@
       </c>
       <c r="G292" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H292" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I292" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -17664,10 +17984,14 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H293" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H293" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -17720,10 +18044,14 @@
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H294" s="4" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H294" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I294" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -17776,10 +18104,14 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H295" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H295" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -17832,10 +18164,14 @@
       </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H296" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H296" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I296" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -17888,10 +18224,14 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H297" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H297" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I297" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -17944,10 +18284,14 @@
       </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H298" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H298" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I298" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -18000,10 +18344,14 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H299" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H299" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I299" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -18056,10 +18404,14 @@
       </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H300" s="4" t="inlineStr"/>
+          <t>0:5</t>
+        </is>
+      </c>
+      <c r="H300" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I300" s="4" t="inlineStr">
         <is>
           <t>受球半</t>
@@ -18112,10 +18464,14 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H301" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H301" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I301" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -18168,10 +18524,14 @@
       </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H302" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H302" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I302" s="4" t="inlineStr">
         <is>
           <t>两球</t>
@@ -18224,10 +18584,14 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H303" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H303" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -18260,7 +18624,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>08-24 04:30</t>
+          <t>08-24 04:40</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -18280,10 +18644,14 @@
       </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H304" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H304" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I304" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -18336,10 +18704,14 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H305" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H305" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I305" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -18392,10 +18764,14 @@
       </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H306" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H306" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I306" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -18448,10 +18824,14 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H307" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H307" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I307" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -18504,10 +18884,14 @@
       </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H308" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H308" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I308" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -18560,10 +18944,14 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H309" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H309" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I309" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -18616,10 +19004,14 @@
       </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H310" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H310" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I310" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -18672,10 +19064,14 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H311" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H311" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I311" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -18708,7 +19104,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>08-24 07:00</t>
+          <t>08-24 07:10</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -18728,10 +19124,14 @@
       </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H312" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H312" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I312" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -18784,10 +19184,14 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H313" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H313" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I313" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -18840,10 +19244,14 @@
       </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H314" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H314" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I314" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -18896,10 +19304,14 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H315" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H315" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I315" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -19124,20 +19536,24 @@
         </is>
       </c>
       <c r="H319" s="5" t="inlineStr"/>
-      <c r="I319" s="5" t="inlineStr"/>
-      <c r="J319" s="5" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="K319" s="5" t="inlineStr">
-        <is>
-          <t>24%</t>
-        </is>
-      </c>
-      <c r="L319" s="7" t="inlineStr">
-        <is>
-          <t>42%</t>
+      <c r="I319" s="5" t="inlineStr">
+        <is>
+          <t>一球/球半</t>
+        </is>
+      </c>
+      <c r="J319" s="7" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="K319" s="7" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="L319" s="5" t="inlineStr">
+        <is>
+          <t>21%</t>
         </is>
       </c>
     </row>
